--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -3331,7 +3331,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F5A6D0-7A31-4094-8370-B6DA888FA816}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{192BE701-BFFD-4EA7-BE4D-74EBE5D86163}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
